--- a/残響時間レポート/残響時間計算表.xlsx
+++ b/残響時間レポート/残響時間計算表.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="203">
   <si>
     <r>
       <rPr>
@@ -252,7 +252,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）の計算。【仮】と書いた面積は図面で確認して直すこと。</t>
+      <t xml:space="preserve">）の計算。「仮定」と書いた面積はレポートにも仮定と明記。</t>
     </r>
   </si>
   <si>
@@ -1164,7 +1164,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">から客席部分を引いた残り</t>
+      <t xml:space="preserve">から客席部分を引いた残り。足音を抑え高音域を吸音</t>
     </r>
   </si>
   <si>
@@ -1218,7 +1218,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">から投光室開口を引いた残り</t>
+      <t xml:space="preserve">から投光室開口を引いた残り。反射面として声を客席後方へ届ける</t>
     </r>
   </si>
   <si>
@@ -1282,7 +1282,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【仮】幅</t>
+      <t xml:space="preserve">仮定：幅</t>
     </r>
     <r>
       <rPr>
@@ -1320,209 +1320,99 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">のスリット開口と仮定→図面で確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">側壁</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[88] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">リブ吸音構造</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">木リブ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">木毛セメント板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スリット</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空気層</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">300</t>
-    </r>
+      <t xml:space="preserve">のスリット開口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">側壁（舞台寄り半分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[21] Wood Panel 9 +GW50 +AS45</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14m×10m×2</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">側壁</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">面から扉を引いた残り</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">後壁</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[48] PW5_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アナアキ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6φ15+GW50 +AS90</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18m×10m</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">扉を除く</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">から調光室ガラスを引いた残り（エコー防止で吸音）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">前壁（舞台側）</t>
-  </si>
-  <si>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18m×10m</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の半分。中高音は反射（初期反射で声を補強）、低音は吸音</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">側壁（客席後方半分）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[52] PW9_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アナアキ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6φ15+GW50 +AS300</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1530,235 +1420,37 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">からプロセニアム開口を引いた残り（反射面）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">プロセニアム開口</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プロセニアム開口</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">扉</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[66] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ドア</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ビニールレザー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">側壁</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【仮】両開き扉 </t>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.8m×2.1m×6</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">扉を除く</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か所→図面で確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">音響・調光室</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[05] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ガラス窓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
         <rFont val="Yu Gothic"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">椅子</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[74] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">椅子</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">モケット張</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">劇場用</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">空席</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1766,8 +1458,16 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【仮】</t>
-    </r>
+      <t xml:space="preserve">の半分。木の有孔板で全帯域を吸音</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">後壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[24] GW25 16K-24K AS375</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1776,7 +1476,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">300</t>
+      <t xml:space="preserve">18m×10m</t>
     </r>
     <r>
       <rPr>
@@ -1785,8 +1485,13 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">席</t>
-    </r>
+      <t xml:space="preserve">から調光室ガラスを引いた残り。強い吸音でエコー防止（表面は布張り）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">前壁（舞台側）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1795,7 +1500,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">×0.5m²/</t>
+      <t xml:space="preserve">18m×10m</t>
     </r>
     <r>
       <rPr>
@@ -1804,7 +1509,281 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">席（客席部分の床面積）→図面で確認</t>
+      <t xml:space="preserve">からプロセニアム開口を引いた残り。反射面</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">プロセニアム開口</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[64] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プロセニアム開口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">扉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[66] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ドア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ビニールレザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仮定：両開き扉 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.8m×2.1m×6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か所。遮音性の高いビニールレザー張り</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">音響・調光室</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[05] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ガラス窓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">椅子</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[74] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">椅子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">モケット張</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">劇場用</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空席</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仮定：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">席</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.5m²/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">席（客席部分の床面積）。人が座った時と吸音の差が小さいモケット張り</t>
     </r>
   </si>
   <si>
@@ -2089,7 +2068,7 @@
     <t xml:space="preserve">建物の用途</t>
   </si>
   <si>
-    <t xml:space="preserve">（ここに用途を記入）</t>
+    <t xml:space="preserve">歌舞伎・演劇（生の声）</t>
   </si>
   <si>
     <r>
@@ -3026,18 +3005,12 @@
     <t xml:space="preserve">[20] Wood Panel 6 +GW50 +AS45</t>
   </si>
   <si>
-    <t xml:space="preserve">[21] Wood Panel 9 +GW50 +AS45</t>
-  </si>
-  <si>
     <t xml:space="preserve">[22] GW25 16K-24K AS0</t>
   </si>
   <si>
     <t xml:space="preserve">[23] GW25 16K-24K AS275</t>
   </si>
   <si>
-    <t xml:space="preserve">[24] GW25 16K-24K AS375</t>
-  </si>
-  <si>
     <t xml:space="preserve">[25] GW25 16K-24K AS475</t>
   </si>
   <si>
@@ -3563,6 +3536,37 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">[48] PW5_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アナアキ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6φ15+GW50 +AS90</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">[49] PW5_</t>
     </r>
     <r>
@@ -3656,7 +3660,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[52] PW9_</t>
+      <t xml:space="preserve">[53] PW9_</t>
     </r>
     <r>
       <rPr>
@@ -3675,19 +3679,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6φ15+GW50 +AS300</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[53] PW9_</t>
+      <t xml:space="preserve">6φ22+GW25 +AS25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[54] PW9_</t>
     </r>
     <r>
       <rPr>
@@ -3706,19 +3710,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6φ22+GW25 +AS25</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[54] PW9_</t>
+      <t xml:space="preserve">6φ22+GW25 +AS150</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[55] PW9_</t>
     </r>
     <r>
       <rPr>
@@ -3737,19 +3741,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6φ22+GW25 +AS150</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[55] PW9_</t>
+      <t xml:space="preserve">6φ22+GW50 +AS150</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[56] PW12_</t>
     </r>
     <r>
       <rPr>
@@ -3768,19 +3772,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6φ22+GW50 +AS150</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[56] PW12_</t>
+      <t xml:space="preserve">6φ15 AS500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[57] PW12_</t>
     </r>
     <r>
       <rPr>
@@ -3799,37 +3803,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6φ15 AS500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[57] PW12_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アナアキ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">6φ15+GW50 +AS500</t>
     </r>
   </si>
@@ -5221,6 +5194,113 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[88] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リブ吸音構造</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">木リブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">木毛セメント板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スリット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空気層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
     </r>
   </si>
   <si>
@@ -6718,22 +6798,22 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.47767003100468</c:v>
+                  <c:v>1.06519905907416</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.24225133406455</c:v>
+                  <c:v>1.02696077682247</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.11583298371305</c:v>
+                  <c:v>1.05569083339879</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.10827689330636</c:v>
+                  <c:v>1.02274076261152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.18021730985388</c:v>
+                  <c:v>1.02806578805118</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.23752196049015</c:v>
+                  <c:v>1.04541541780318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6832,22 +6912,22 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.3934103303129</c:v>
+                  <c:v>1.02070574511519</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1873770511114</c:v>
+                  <c:v>0.989169186202267</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0713591061804</c:v>
+                  <c:v>1.01579623611216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.06439145952567</c:v>
+                  <c:v>0.985253453518616</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.13057717759483</c:v>
+                  <c:v>0.990194325636406</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.18305554610102</c:v>
+                  <c:v>1.00627926246119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6862,11 +6942,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="16078373"/>
-        <c:axId val="73242429"/>
+        <c:axId val="45302173"/>
+        <c:axId val="58974264"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16078373"/>
+        <c:axId val="45302173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6932,7 +7012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73242429"/>
+        <c:crossAx val="58974264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6940,7 +7020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73242429"/>
+        <c:axId val="58974264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -7018,7 +7098,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16078373"/>
+        <c:crossAx val="45302173"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.5"/>
@@ -7352,11 +7432,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="69485285"/>
-        <c:axId val="53150540"/>
+        <c:axId val="83390138"/>
+        <c:axId val="29473262"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69485285"/>
+        <c:axId val="83390138"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7422,7 +7502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53150540"/>
+        <c:crossAx val="29473262"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7430,7 +7510,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53150540"/>
+        <c:axId val="29473262"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -7508,7 +7588,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69485285"/>
+        <c:crossAx val="83390138"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.5"/>
@@ -8060,7 +8140,7 @@
         <v>37</v>
       </c>
       <c r="D6" s="11" t="n">
-        <f aca="false">252-D15</f>
+        <f aca="false">252-D16</f>
         <v>102</v>
       </c>
       <c r="E6" s="12" t="n">
@@ -8258,58 +8338,58 @@
         <v>37</v>
       </c>
       <c r="D9" s="11" t="n">
-        <f aca="false">14*10*2-D13</f>
-        <v>257.32</v>
+        <f aca="false">(14*10*2-D14)/2</f>
+        <v>128.66</v>
       </c>
       <c r="E9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*E9,""))</f>
-        <v>115.794</v>
+        <v>61.7568</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="H9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*G9,""))</f>
-        <v>128.66</v>
+        <v>23.1588</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="J9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*I9,""))</f>
-        <v>95.2084</v>
+        <v>12.866</v>
       </c>
       <c r="K9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="L9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*K9,""))</f>
-        <v>102.928</v>
+        <v>10.2928</v>
       </c>
       <c r="M9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*M9,""))</f>
-        <v>102.928</v>
+        <v>10.2928</v>
       </c>
       <c r="O9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B9,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="P9" s="12" t="n">
         <f aca="false">IF(OR($B9="",$D9=""),"",IFERROR($D9*O9,""))</f>
-        <v>95.2084</v>
-      </c>
-      <c r="Q9" s="14" t="s">
+        <v>12.866</v>
+      </c>
+      <c r="Q9" s="13" t="s">
         <v>47</v>
       </c>
     </row>
@@ -8324,24 +8404,24 @@
         <v>37</v>
       </c>
       <c r="D10" s="11" t="n">
-        <f aca="false">18*10-D14</f>
-        <v>165</v>
+        <f aca="false">(14*10*2-D14)/2</f>
+        <v>128.66</v>
       </c>
       <c r="E10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*E10,""))</f>
-        <v>33</v>
+        <v>77.196</v>
       </c>
       <c r="G10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*G10,""))</f>
-        <v>74.25</v>
+        <v>115.794</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
@@ -8349,33 +8429,33 @@
       </c>
       <c r="J10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*I10,""))</f>
-        <v>132</v>
+        <v>102.928</v>
       </c>
       <c r="K10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*K10,""))</f>
-        <v>99</v>
+        <v>90.062</v>
       </c>
       <c r="M10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*M10,""))</f>
-        <v>66</v>
+        <v>77.196</v>
       </c>
       <c r="O10" s="12" t="n">
         <f aca="false">IF($B10="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B10,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="P10" s="12" t="n">
         <f aca="false">IF(OR($B10="",$D10=""),"",IFERROR($D10*O10,""))</f>
-        <v>49.5</v>
-      </c>
-      <c r="Q10" s="14" t="s">
+        <v>51.464</v>
+      </c>
+      <c r="Q10" s="13" t="s">
         <v>50</v>
       </c>
     </row>
@@ -8384,194 +8464,194 @@
         <v>51</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="11" t="n">
-        <f aca="false">18*10-D12</f>
-        <v>96</v>
+        <f aca="false">18*10-D15</f>
+        <v>165</v>
       </c>
       <c r="E11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*E11,""))</f>
-        <v>19.2</v>
+        <v>115.5</v>
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.12</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*G11,""))</f>
-        <v>11.52</v>
+        <v>132</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*I11,""))</f>
-        <v>7.68</v>
+        <v>132</v>
       </c>
       <c r="K11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.07</v>
+        <v>0.8</v>
       </c>
       <c r="L11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*K11,""))</f>
-        <v>6.72</v>
+        <v>132</v>
       </c>
       <c r="M11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.07</v>
+        <v>0.8</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*M11,""))</f>
-        <v>6.72</v>
+        <v>132</v>
       </c>
       <c r="O11" s="12" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B11,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.08</v>
+        <v>0.85</v>
       </c>
       <c r="P11" s="12" t="n">
         <f aca="false">IF(OR($B11="",$D11=""),"",IFERROR($D11*O11,""))</f>
-        <v>7.68</v>
+        <v>140.25</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="11" t="n">
+        <f aca="false">18*10-D13</f>
+        <v>96</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.2</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*E12,""))</f>
+        <v>19.2</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.12</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*G12,""))</f>
+        <v>11.52</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.08</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*I12,""))</f>
+        <v>7.68</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.07</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*K12,""))</f>
+        <v>6.72</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.07</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*M12,""))</f>
+        <v>6.72</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.08</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*O12,""))</f>
+        <v>7.68</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <f aca="false">12*7</f>
         <v>84</v>
       </c>
-      <c r="E12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*E12,""))</f>
-        <v>25.2</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.35</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*G12,""))</f>
-        <v>29.4</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*I12,""))</f>
-        <v>33.6</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.45</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*K12,""))</f>
-        <v>37.8</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.5</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*M12,""))</f>
-        <v>42</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B12,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.55</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <f aca="false">IF(OR($B12="",$D12=""),"",IFERROR($D12*O12,""))</f>
-        <v>46.2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <f aca="false">6*1.8*2.1</f>
-        <v>22.68</v>
-      </c>
       <c r="E13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*E13,""))</f>
-        <v>2.268</v>
+        <v>25.2</v>
       </c>
       <c r="G13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*G13,""))</f>
-        <v>3.402</v>
+        <v>29.4</v>
       </c>
       <c r="I13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*I13,""))</f>
-        <v>4.536</v>
+        <v>33.6</v>
       </c>
       <c r="K13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*K13,""))</f>
-        <v>5.67</v>
+        <v>37.8</v>
       </c>
       <c r="M13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*M13,""))</f>
-        <v>6.804</v>
+        <v>42</v>
       </c>
       <c r="O13" s="12" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B13,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="P13" s="12" t="n">
         <f aca="false">IF(OR($B13="",$D13=""),"",IFERROR($D13*O13,""))</f>
-        <v>6.804</v>
-      </c>
-      <c r="Q13" s="13" t="s">
-        <v>57</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8585,242 +8665,254 @@
         <v>37</v>
       </c>
       <c r="D14" s="11" t="n">
+        <f aca="false">6*1.8*2.1</f>
+        <v>22.68</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*E14,""))</f>
+        <v>2.268</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.15</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*G14,""))</f>
+        <v>3.402</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.2</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*I14,""))</f>
+        <v>4.536</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.25</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*K14,""))</f>
+        <v>5.67</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.3</v>
+      </c>
+      <c r="N14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*M14,""))</f>
+        <v>6.804</v>
+      </c>
+      <c r="O14" s="12" t="n">
+        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.3</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*O14,""))</f>
+        <v>6.804</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <f aca="false">10*1.5</f>
         <v>15</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="E15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.18</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*E14,""))</f>
+      <c r="F15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*E15,""))</f>
         <v>2.7</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="G15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.06</v>
       </c>
-      <c r="H14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*G14,""))</f>
+      <c r="H15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*G15,""))</f>
         <v>0.9</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="I15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.04</v>
       </c>
-      <c r="J14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*I14,""))</f>
+      <c r="J15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*I15,""))</f>
         <v>0.6</v>
       </c>
-      <c r="K14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="K15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.03</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*K14,""))</f>
+      <c r="L15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*K15,""))</f>
         <v>0.45</v>
       </c>
-      <c r="M14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="M15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.02</v>
       </c>
-      <c r="N14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*M14,""))</f>
+      <c r="N15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*M15,""))</f>
         <v>0.3</v>
       </c>
-      <c r="O14" s="12" t="n">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B14,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+      <c r="O15" s="12" t="n">
+        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
         <v>0.02</v>
       </c>
-      <c r="P14" s="12" t="n">
-        <f aca="false">IF(OR($B14="",$D14=""),"",IFERROR($D14*O14,""))</f>
+      <c r="P15" s="12" t="n">
+        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*O15,""))</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="11" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="11" t="n">
         <f aca="false">300*0.5</f>
         <v>150</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.14</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*E15,""))</f>
-        <v>21</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.25</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*G15,""))</f>
-        <v>37.5</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*I15,""))</f>
-        <v>45</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*K15,""))</f>
-        <v>45</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*M15,""))</f>
-        <v>45</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B15,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.3</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <f aca="false">IF(OR($B15="",$D15=""),"",IFERROR($D15*O15,""))</f>
-        <v>45</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <f aca="false">D15</f>
-        <v>150</v>
-      </c>
       <c r="E16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*E16,""))</f>
-        <v>37.5</v>
+        <v>21</v>
       </c>
       <c r="G16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*G16,""))</f>
-        <v>52.5</v>
+        <v>37.5</v>
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*I16,""))</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*K16,""))</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*M16,""))</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O16" s="12" t="n">
         <f aca="false">IF($B16="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B16,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P16" s="12" t="n">
         <f aca="false">IF(OR($B16="",$D16=""),"",IFERROR($D16*O16,""))</f>
+        <v>45</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <f aca="false">D16</f>
+        <v>150</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*E17,""))</f>
+        <v>37.5</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.35</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*G17,""))</f>
+        <v>52.5</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
+        <v>0.4</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*I17,""))</f>
         <v>60</v>
       </c>
-      <c r="Q16" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12" t="str">
-        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!C$5:C$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="F17" s="12" t="str">
-        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*E17,""))</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="str">
-        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!D$5:D$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="H17" s="12" t="str">
-        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*G17,""))</f>
-        <v/>
-      </c>
-      <c r="I17" s="12" t="str">
-        <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!E$5:E$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="J17" s="12" t="str">
-        <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*I17,""))</f>
-        <v/>
-      </c>
-      <c r="K17" s="12" t="str">
+      <c r="K17" s="12" t="n">
         <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!F$5:F$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="L17" s="12" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*K17,""))</f>
-        <v/>
-      </c>
-      <c r="M17" s="12" t="str">
+        <v>60</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!G$5:G$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="N17" s="12" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*M17,""))</f>
-        <v/>
-      </c>
-      <c r="O17" s="12" t="str">
+        <v>60</v>
+      </c>
+      <c r="O17" s="12" t="n">
         <f aca="false">IF($B17="","",IFERROR(INDEX(材料DB!H$5:H$130,MATCH($B17,材料DB!$B$5:$B$130,0)),"材料なし"))</f>
-        <v/>
-      </c>
-      <c r="P17" s="12" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="P17" s="12" t="n">
         <f aca="false">IF(OR($B17="",$D17=""),"",IFERROR($D17*O17,""))</f>
-        <v/>
+        <v>60</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9257,301 +9349,305 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D27" s="15" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",$D$6:$D$25)</f>
         <v>994</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I27" s="15" t="n">
         <f aca="false">D27+SUMIF($C$6:$C$25,"空席",$D$6:$D$25)</f>
         <v>1144</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>2520</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",F$6:F$25)+SUMIF($C$6:$C$25,"空席",F$6:F$25)</f>
-        <v>272.862</v>
+        <v>378.5208</v>
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",H$6:H$25)+SUMIF($C$6:$C$25,"空席",H$6:H$25)</f>
-        <v>324.572</v>
+        <v>392.6148</v>
       </c>
       <c r="J30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",J$6:J$25)+SUMIF($C$6:$C$25,"空席",J$6:J$25)</f>
-        <v>361.3444</v>
+        <v>381.93</v>
       </c>
       <c r="L30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",L$6:L$25)+SUMIF($C$6:$C$25,"空席",L$6:L$25)</f>
-        <v>363.808</v>
+        <v>394.2348</v>
       </c>
       <c r="N30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",N$6:N$25)+SUMIF($C$6:$C$25,"空席",N$6:N$25)</f>
-        <v>341.632</v>
+        <v>392.1928</v>
       </c>
       <c r="P30" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",P$6:P$25)+SUMIF($C$6:$C$25,"空席",P$6:P$25)</f>
-        <v>325.8124</v>
+        <v>385.684</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",F$6:F$25)+SUMIF($C$6:$C$25,"満席",F$6:F$25)</f>
-        <v>289.362</v>
+        <v>395.0208</v>
       </c>
       <c r="H31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",H$6:H$25)+SUMIF($C$6:$C$25,"満席",H$6:H$25)</f>
-        <v>339.572</v>
+        <v>407.6148</v>
       </c>
       <c r="J31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",J$6:J$25)+SUMIF($C$6:$C$25,"満席",J$6:J$25)</f>
-        <v>376.3444</v>
+        <v>396.93</v>
       </c>
       <c r="L31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",L$6:L$25)+SUMIF($C$6:$C$25,"満席",L$6:L$25)</f>
-        <v>378.808</v>
+        <v>409.2348</v>
       </c>
       <c r="N31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",N$6:N$25)+SUMIF($C$6:$C$25,"満席",N$6:N$25)</f>
-        <v>356.632</v>
+        <v>407.1928</v>
       </c>
       <c r="P31" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$25,"共通",P$6:P$25)+SUMIF($C$6:$C$25,"満席",P$6:P$25)</f>
-        <v>340.8124</v>
+        <v>400.684</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F32" s="20" t="n">
         <f aca="false">IF(OR(F30=0,$D$28=""),"",0.16*$D$28/F30)</f>
-        <v>1.47767003100468</v>
+        <v>1.06519905907416</v>
       </c>
       <c r="H32" s="20" t="n">
         <f aca="false">IF(OR(H30=0,$D$28=""),"",0.16*$D$28/H30)</f>
-        <v>1.24225133406455</v>
+        <v>1.02696077682247</v>
       </c>
       <c r="J32" s="20" t="n">
         <f aca="false">IF(OR(J30=0,$D$28=""),"",0.16*$D$28/J30)</f>
-        <v>1.11583298371305</v>
+        <v>1.05569083339879</v>
       </c>
       <c r="L32" s="20" t="n">
         <f aca="false">IF(OR(L30=0,$D$28=""),"",0.16*$D$28/L30)</f>
-        <v>1.10827689330636</v>
+        <v>1.02274076261152</v>
       </c>
       <c r="N32" s="20" t="n">
         <f aca="false">IF(OR(N30=0,$D$28=""),"",0.16*$D$28/N30)</f>
-        <v>1.18021730985388</v>
+        <v>1.02806578805118</v>
       </c>
       <c r="P32" s="20" t="n">
         <f aca="false">IF(OR(P30=0,$D$28=""),"",0.16*$D$28/P30)</f>
-        <v>1.23752196049015</v>
+        <v>1.04541541780318</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F33" s="20" t="n">
         <f aca="false">IF(OR(F31=0,$D$28=""),"",0.16*$D$28/F31)</f>
-        <v>1.3934103303129</v>
+        <v>1.02070574511519</v>
       </c>
       <c r="H33" s="20" t="n">
         <f aca="false">IF(OR(H31=0,$D$28=""),"",0.16*$D$28/H31)</f>
-        <v>1.1873770511114</v>
+        <v>0.989169186202267</v>
       </c>
       <c r="J33" s="20" t="n">
         <f aca="false">IF(OR(J31=0,$D$28=""),"",0.16*$D$28/J31)</f>
-        <v>1.0713591061804</v>
+        <v>1.01579623611216</v>
       </c>
       <c r="L33" s="20" t="n">
         <f aca="false">IF(OR(L31=0,$D$28=""),"",0.16*$D$28/L31)</f>
-        <v>1.06439145952567</v>
+        <v>0.985253453518616</v>
       </c>
       <c r="N33" s="20" t="n">
         <f aca="false">IF(OR(N31=0,$D$28=""),"",0.16*$D$28/N31)</f>
-        <v>1.13057717759483</v>
+        <v>0.990194325636406</v>
       </c>
       <c r="P33" s="20" t="n">
         <f aca="false">IF(OR(P31=0,$D$28=""),"",0.16*$D$28/P31)</f>
-        <v>1.18305554610102</v>
+        <v>1.00627926246119</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B38" s="23" t="n">
         <f aca="false">F32</f>
-        <v>1.47767003100468</v>
+        <v>1.06519905907416</v>
       </c>
       <c r="C38" s="23" t="n">
         <f aca="false">F33</f>
-        <v>1.3934103303129</v>
+        <v>1.02070574511519</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B39" s="23" t="n">
         <f aca="false">H32</f>
-        <v>1.24225133406455</v>
+        <v>1.02696077682247</v>
       </c>
       <c r="C39" s="23" t="n">
         <f aca="false">H33</f>
-        <v>1.1873770511114</v>
+        <v>0.989169186202267</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B40" s="23" t="n">
         <f aca="false">J32</f>
-        <v>1.11583298371305</v>
+        <v>1.05569083339879</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">J33</f>
-        <v>1.0713591061804</v>
+        <v>1.01579623611216</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B41" s="23" t="n">
         <f aca="false">L32</f>
-        <v>1.10827689330636</v>
+        <v>1.02274076261152</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">L33</f>
-        <v>1.06439145952567</v>
+        <v>0.985253453518616</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">N32</f>
-        <v>1.18021730985388</v>
+        <v>1.02806578805118</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">N33</f>
-        <v>1.13057717759483</v>
+        <v>0.990194325636406</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B43" s="23" t="n">
         <f aca="false">P32</f>
-        <v>1.23752196049015</v>
+        <v>1.04541541780318</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">P33</f>
-        <v>1.18305554610102</v>
+        <v>1.00627926246119</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="25"/>
+        <v>92</v>
+      </c>
+      <c r="D54" s="25" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D55" s="25"/>
+        <v>93</v>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D56" s="26" t="n">
         <f aca="false">J33</f>
-        <v>1.0713591061804</v>
+        <v>1.01579623611216</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D57" s="0" t="str">
         <f aca="false">IF(OR(D54="",D55="",D56=""),"最適値を入力してください",IF(AND(D56&gt;=D54,D56&lt;=D55),"範囲内 OK",IF(D56&gt;D55,"長すぎ → 吸音を増やす","短すぎ → 吸音を減らす")))</f>
-        <v>最適値を入力してください</v>
+        <v>範囲内 OK</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -9605,20 +9701,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>26</v>
@@ -9639,7 +9735,7 @@
         <v>31</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9647,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>0.01</v>
@@ -9668,7 +9764,7 @@
         <v>0.03</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9676,7 +9772,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>0.03</v>
@@ -9697,7 +9793,7 @@
         <v>0.08</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9705,7 +9801,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>0.04</v>
@@ -9726,7 +9822,7 @@
         <v>0.2</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9734,7 +9830,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>0.12</v>
@@ -9755,7 +9851,7 @@
         <v>0.27</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9763,7 +9859,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0.18</v>
@@ -9784,7 +9880,7 @@
         <v>0.02</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9792,7 +9888,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>0.04</v>
@@ -9813,7 +9909,7 @@
         <v>0.02</v>
       </c>
       <c r="I10" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9821,7 +9917,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C11" s="28" t="n">
         <v>0.02</v>
@@ -9842,7 +9938,7 @@
         <v>0.15</v>
       </c>
       <c r="I11" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9850,7 +9946,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>0.02</v>
@@ -9871,7 +9967,7 @@
         <v>0.4</v>
       </c>
       <c r="I12" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9900,7 +9996,7 @@
         <v>0.5</v>
       </c>
       <c r="I13" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9908,7 +10004,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" s="28" t="n">
         <v>0.26</v>
@@ -9929,7 +10025,7 @@
         <v>0.26</v>
       </c>
       <c r="I14" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9937,7 +10033,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>0.28</v>
@@ -9958,7 +10054,7 @@
         <v>0.35</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9966,7 +10062,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>0.15</v>
@@ -9987,7 +10083,7 @@
         <v>0.35</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9995,7 +10091,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>0.15</v>
@@ -10016,7 +10112,7 @@
         <v>0.08</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10024,7 +10120,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>0.04</v>
@@ -10045,7 +10141,7 @@
         <v>0.07</v>
       </c>
       <c r="I18" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10053,7 +10149,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>0.15</v>
@@ -10074,7 +10170,7 @@
         <v>0.06</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10082,7 +10178,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>0.18</v>
@@ -10103,7 +10199,7 @@
         <v>0.08</v>
       </c>
       <c r="I20" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10111,7 +10207,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C21" s="28" t="n">
         <v>0.22</v>
@@ -10132,7 +10228,7 @@
         <v>0.08</v>
       </c>
       <c r="I21" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10140,7 +10236,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>0.11</v>
@@ -10161,7 +10257,7 @@
         <v>0.08</v>
       </c>
       <c r="I22" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10190,7 +10286,7 @@
         <v>0.08</v>
       </c>
       <c r="I23" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10198,7 +10294,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C24" s="28" t="n">
         <v>0.41</v>
@@ -10219,7 +10315,7 @@
         <v>0.12</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10227,7 +10323,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="C25" s="28" t="n">
         <v>0.48</v>
@@ -10248,7 +10344,7 @@
         <v>0.1</v>
       </c>
       <c r="I25" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10256,7 +10352,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C26" s="28" t="n">
         <v>0.1</v>
@@ -10277,7 +10373,7 @@
         <v>0.85</v>
       </c>
       <c r="I26" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10285,7 +10381,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="28" t="n">
         <v>0.6</v>
@@ -10306,7 +10402,7 @@
         <v>0.85</v>
       </c>
       <c r="I27" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10314,7 +10410,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="C28" s="28" t="n">
         <v>0.7</v>
@@ -10335,7 +10431,7 @@
         <v>0.85</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10343,7 +10439,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" s="28" t="n">
         <v>0.75</v>
@@ -10364,7 +10460,7 @@
         <v>0.9</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10372,7 +10468,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="28" t="n">
         <v>0.11</v>
@@ -10393,7 +10489,7 @@
         <v>0.86</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10401,7 +10497,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" s="28" t="n">
         <v>0.7</v>
@@ -10422,7 +10518,7 @@
         <v>0.85</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10430,7 +10526,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" s="28" t="n">
         <v>0.75</v>
@@ -10451,7 +10547,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10459,7 +10555,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" s="28" t="n">
         <v>0.4</v>
@@ -10480,7 +10576,7 @@
         <v>0.9</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10488,7 +10584,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" s="28" t="n">
         <v>0.5</v>
@@ -10509,7 +10605,7 @@
         <v>0.9</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10517,7 +10613,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" s="28" t="n">
         <v>0.06</v>
@@ -10538,7 +10634,7 @@
         <v>0.82</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10546,7 +10642,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36" s="28" t="n">
         <v>0.3</v>
@@ -10567,7 +10663,7 @@
         <v>0.87</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10575,7 +10671,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" s="28" t="n">
         <v>0.47</v>
@@ -10596,7 +10692,7 @@
         <v>0.8</v>
       </c>
       <c r="I37" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10604,7 +10700,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C38" s="28" t="n">
         <v>0.33</v>
@@ -10625,7 +10721,7 @@
         <v>0.89</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10633,7 +10729,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C39" s="28" t="n">
         <v>0.7</v>
@@ -10654,7 +10750,7 @@
         <v>0.92</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10662,7 +10758,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" s="28" t="n">
         <v>0.02</v>
@@ -10683,7 +10779,7 @@
         <v>0.1</v>
       </c>
       <c r="I40" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10691,7 +10787,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" s="28" t="n">
         <v>0.07</v>
@@ -10712,7 +10808,7 @@
         <v>0.12</v>
       </c>
       <c r="I41" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10720,7 +10816,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C42" s="28" t="n">
         <v>0.12</v>
@@ -10741,7 +10837,7 @@
         <v>0.16</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10749,7 +10845,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C43" s="28" t="n">
         <v>0.45</v>
@@ -10770,7 +10866,7 @@
         <v>0.28</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10778,7 +10874,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" s="28" t="n">
         <v>0.02</v>
@@ -10799,7 +10895,7 @@
         <v>0.18</v>
       </c>
       <c r="I44" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10807,7 +10903,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C45" s="28" t="n">
         <v>0.06</v>
@@ -10828,7 +10924,7 @@
         <v>0.12</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10836,7 +10932,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C46" s="28" t="n">
         <v>0.11</v>
@@ -10857,7 +10953,7 @@
         <v>0.13</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10865,7 +10961,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C47" s="28" t="n">
         <v>0.35</v>
@@ -10886,7 +10982,7 @@
         <v>0.39</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10894,7 +10990,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C48" s="28" t="n">
         <v>0.15</v>
@@ -10915,7 +11011,7 @@
         <v>0.2</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10923,7 +11019,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" s="28" t="n">
         <v>0.2</v>
@@ -10944,7 +11040,7 @@
         <v>0.15</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10952,7 +11048,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" s="28" t="n">
         <v>0.4</v>
@@ -10973,7 +11069,7 @@
         <v>0.1</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10981,7 +11077,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" s="28" t="n">
         <v>0.13</v>
@@ -11002,7 +11098,7 @@
         <v>0.31</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11010,7 +11106,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C52" s="28" t="n">
         <v>0.2</v>
@@ -11031,7 +11127,7 @@
         <v>0.3</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11039,7 +11135,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C53" s="28" t="n">
         <v>0.3</v>
@@ -11060,7 +11156,7 @@
         <v>0.25</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11068,7 +11164,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C54" s="28" t="n">
         <v>0.35</v>
@@ -11089,7 +11185,7 @@
         <v>0.4</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11097,7 +11193,7 @@
         <v>51</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C55" s="28" t="n">
         <v>0.55</v>
@@ -11118,7 +11214,7 @@
         <v>0.4</v>
       </c>
       <c r="I55" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11126,7 +11222,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="C56" s="28" t="n">
         <v>0.6</v>
@@ -11147,7 +11243,7 @@
         <v>0.4</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11155,7 +11251,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C57" s="28" t="n">
         <v>0.2</v>
@@ -11176,7 +11272,7 @@
         <v>0.2</v>
       </c>
       <c r="I57" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11184,7 +11280,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C58" s="28" t="n">
         <v>0.4</v>
@@ -11205,7 +11301,7 @@
         <v>0.3</v>
       </c>
       <c r="I58" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11213,7 +11309,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C59" s="28" t="n">
         <v>0.55</v>
@@ -11234,7 +11330,7 @@
         <v>0.3</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11242,7 +11338,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60" s="28" t="n">
         <v>0.35</v>
@@ -11263,7 +11359,7 @@
         <v>0.3</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11271,7 +11367,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C61" s="28" t="n">
         <v>0.9</v>
@@ -11292,7 +11388,7 @@
         <v>0.4</v>
       </c>
       <c r="I61" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11300,7 +11396,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C62" s="28" t="n">
         <v>0.45</v>
@@ -11321,7 +11417,7 @@
         <v>0.7</v>
       </c>
       <c r="I62" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11329,7 +11425,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C63" s="28" t="n">
         <v>0.5</v>
@@ -11350,7 +11446,7 @@
         <v>0.7</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11358,7 +11454,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64" s="28" t="n">
         <v>0.6</v>
@@ -11379,7 +11475,7 @@
         <v>0.7</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11408,7 +11504,7 @@
         <v>0.3</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11416,7 +11512,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C66" s="28" t="n">
         <v>0.25</v>
@@ -11437,7 +11533,7 @@
         <v>0.6</v>
       </c>
       <c r="I66" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11445,7 +11541,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C67" s="28" t="n">
         <v>0.75</v>
@@ -11466,7 +11562,7 @@
         <v>0.85</v>
       </c>
       <c r="I67" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11474,7 +11570,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C68" s="28" t="n">
         <v>0.3</v>
@@ -11495,7 +11591,7 @@
         <v>0.55</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11503,7 +11599,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C69" s="28" t="n">
         <v>0.13</v>
@@ -11524,7 +11620,7 @@
         <v>0.04</v>
       </c>
       <c r="I69" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11532,7 +11628,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C70" s="28" t="n">
         <v>0.1</v>
@@ -11553,7 +11649,7 @@
         <v>0.3</v>
       </c>
       <c r="I70" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11561,7 +11657,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="28" t="n">
         <v>0.03</v>
@@ -11582,7 +11678,7 @@
         <v>0.08</v>
       </c>
       <c r="I71" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11590,7 +11686,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C72" s="28" t="n">
         <v>0.04</v>
@@ -11611,7 +11707,7 @@
         <v>0.27</v>
       </c>
       <c r="I72" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11619,7 +11715,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" s="28" t="n">
         <v>0.06</v>
@@ -11640,7 +11736,7 @@
         <v>0.35</v>
       </c>
       <c r="I73" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11648,7 +11744,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C74" s="28" t="n">
         <v>0.15</v>
@@ -11669,7 +11765,7 @@
         <v>0.65</v>
       </c>
       <c r="I74" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11677,7 +11773,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C75" s="28" t="n">
         <v>0.04</v>
@@ -11698,7 +11794,7 @@
         <v>0.4</v>
       </c>
       <c r="I75" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11706,7 +11802,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C76" s="28" t="n">
         <v>0.07</v>
@@ -11727,7 +11823,7 @@
         <v>0.54</v>
       </c>
       <c r="I76" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11735,7 +11831,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C77" s="28" t="n">
         <v>0.05</v>
@@ -11756,7 +11852,7 @@
         <v>0.7</v>
       </c>
       <c r="I77" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11764,7 +11860,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C78" s="28" t="n">
         <v>0.14</v>
@@ -11785,7 +11881,7 @@
         <v>0.3</v>
       </c>
       <c r="I78" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11793,7 +11889,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C79" s="28" t="n">
         <v>0.04</v>
@@ -11814,7 +11910,7 @@
         <v>0.11</v>
       </c>
       <c r="I79" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11822,7 +11918,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C80" s="28" t="n">
         <v>0.02</v>
@@ -11843,7 +11939,7 @@
         <v>0.03</v>
       </c>
       <c r="I80" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11851,7 +11947,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C81" s="28" t="n">
         <v>0.21</v>
@@ -11872,7 +11968,7 @@
         <v>0.41</v>
       </c>
       <c r="I81" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11880,7 +11976,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C82" s="28" t="n">
         <v>0.25</v>
@@ -11901,7 +11997,7 @@
         <v>0.4</v>
       </c>
       <c r="I82" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11909,7 +12005,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" s="28" t="n">
         <v>0.19</v>
@@ -11930,7 +12026,7 @@
         <v>0.38</v>
       </c>
       <c r="I83" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11938,7 +12034,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C84" s="28" t="n">
         <v>0.08</v>
@@ -11959,7 +12055,7 @@
         <v>0.15</v>
       </c>
       <c r="I84" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11967,7 +12063,7 @@
         <v>81</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C85" s="28" t="n">
         <v>0.22</v>
@@ -11988,7 +12084,7 @@
         <v>0.12</v>
       </c>
       <c r="I85" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11996,7 +12092,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C86" s="28" t="n">
         <v>0.07</v>
@@ -12017,7 +12113,7 @@
         <v>0.17</v>
       </c>
       <c r="I86" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12025,7 +12121,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C87" s="28" t="n">
         <v>0.12</v>
@@ -12046,7 +12142,7 @@
         <v>0.15</v>
       </c>
       <c r="I87" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12054,7 +12150,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C88" s="28" t="n">
         <v>0.18</v>
@@ -12075,7 +12171,7 @@
         <v>0.26</v>
       </c>
       <c r="I88" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12083,7 +12179,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C89" s="28" t="n">
         <v>0.12</v>
@@ -12104,7 +12200,7 @@
         <v>0.22</v>
       </c>
       <c r="I89" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12112,7 +12208,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C90" s="28" t="n">
         <v>0.15</v>
@@ -12133,7 +12229,7 @@
         <v>0.12</v>
       </c>
       <c r="I90" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12141,7 +12237,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C91" s="28" t="n">
         <v>0.1</v>
@@ -12162,7 +12258,7 @@
         <v>0.3</v>
       </c>
       <c r="I91" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12170,7 +12266,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c r="C92" s="28" t="n">
         <v>0.45</v>
@@ -12191,7 +12287,7 @@
         <v>0.37</v>
       </c>
       <c r="I92" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12199,7 +12295,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C93" s="28" t="n">
         <v>0.08</v>
@@ -12220,7 +12316,7 @@
         <v>0.38</v>
       </c>
       <c r="I93" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12228,7 +12324,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C94" s="28" t="n">
         <v>0.37</v>
@@ -12249,7 +12345,7 @@
         <v>0.44</v>
       </c>
       <c r="I94" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12257,7 +12353,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C95" s="28" t="n">
         <v>0.25</v>
@@ -12278,7 +12374,7 @@
         <v>0.44</v>
       </c>
       <c r="I95" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12286,7 +12382,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C96" s="28" t="n">
         <v>0.68</v>
@@ -12307,7 +12403,7 @@
         <v>0.5</v>
       </c>
       <c r="I96" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12315,7 +12411,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C97" s="28" t="n">
         <v>0.65</v>
@@ -12336,7 +12432,7 @@
         <v>0.4</v>
       </c>
       <c r="I97" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12344,7 +12440,7 @@
         <v>94</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C98" s="28" t="n">
         <v>0.2</v>
@@ -12365,7 +12461,7 @@
         <v>0.6</v>
       </c>
       <c r="I98" s="29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12749,7 +12845,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12842,10 +12938,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>37</v>
@@ -12907,7 +13003,7 @@
         <v>39</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>37</v>
@@ -12964,7 +13060,7 @@
         <v>33.84</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13031,7 +13127,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>40</v>
@@ -13091,15 +13187,15 @@
         <v>19.2</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>37</v>
@@ -13156,15 +13252,15 @@
         <v>19.52</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>37</v>
@@ -13223,10 +13319,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>37</v>
@@ -13285,10 +13381,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>37</v>
@@ -13347,13 +13443,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>518</v>
@@ -13409,13 +13505,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" s="34" t="n">
         <v>518</v>
@@ -13471,43 +13567,43 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">SUMIF($C$6:$C$15,"共通",$D$6:$D$15)</f>
         <v>1415</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I17" s="15" t="n">
         <f aca="false">D17+SUMIF($C$6:$C$15,"空席",$D$6:$D$15)</f>
         <v>1933</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D18" s="35" t="n">
         <v>2649</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F20" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$15,"共通",F$6:F$15)+SUMIF($C$6:$C$15,"空席",F$6:F$15)</f>
@@ -13537,7 +13633,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" s="19" t="n">
         <f aca="false">SUMIF($C$6:$C$15,"共通",F$6:F$15)+SUMIF($C$6:$C$15,"満席",F$6:F$15)</f>
@@ -13566,10 +13662,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F22" s="20" t="n">
         <f aca="false">IF(OR(F20=0,$D$18=""),"",0.16*$D$18/F20)</f>
@@ -13599,7 +13695,7 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F23" s="20" t="n">
         <f aca="false">IF(OR(F21=0,$D$18=""),"",0.16*$D$18/F21)</f>
@@ -13628,23 +13724,23 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">F22</f>
@@ -13657,7 +13753,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">H22</f>
@@ -13670,7 +13766,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">J22</f>
@@ -13683,7 +13779,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">L22</f>
@@ -13696,7 +13792,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">N22</f>
@@ -13709,7 +13805,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">P22</f>
@@ -13722,12 +13818,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="36" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F44" s="37" t="n">
         <v>279.62</v>
@@ -13750,7 +13846,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F45" s="38" t="str">
         <f aca="false">IF(ABS(F20-F44)&lt;=0.011,"OK","ズレ")</f>
@@ -13779,7 +13875,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F46" s="37" t="n">
         <v>336.6</v>
@@ -13802,7 +13898,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F47" s="38" t="str">
         <f aca="false">IF(ABS(F21-F46)&lt;=0.011,"OK","ズレ")</f>
@@ -13831,7 +13927,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F48" s="37" t="n">
         <v>1.52</v>
@@ -13854,7 +13950,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F49" s="38" t="str">
         <f aca="false">IF(ABS(F22-F48)&lt;=0.011,"OK","ズレ")</f>
@@ -13883,7 +13979,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F50" s="37" t="n">
         <v>1.26</v>
@@ -13906,7 +14002,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F51" s="38" t="str">
         <f aca="false">IF(ABS(F23-F50)&lt;=0.011,"OK","ズレ")</f>
@@ -13935,7 +14031,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
